--- a/AAII_Financials/Quarterly/PLD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PLD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
   <si>
     <t>PLD</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2572900</v>
+      </c>
+      <c r="E8" s="3">
         <v>2391000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2386800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2306700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2291600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2207600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2294700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2121100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2110300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2029100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1978700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1986000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2521600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1844400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1751600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1750900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1252100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1219100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1277200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1183000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1150800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1148300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1111600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1082800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1266100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>978200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>826000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>942200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>790400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>772100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>807100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>682400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>621300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>693700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>619900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>602900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>766200</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>629200</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>620100</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>704600</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>626500</v>
+      </c>
+      <c r="E9" s="3">
         <v>602200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>578800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>553900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>552900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>549100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>519600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>488800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>515800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>533100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>487100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>500100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>538800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>484300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>438800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>415300</v>
-      </c>
-      <c r="S9" s="3">
-        <v>327500</v>
       </c>
       <c r="T9" s="3">
         <v>327500</v>
       </c>
       <c r="U9" s="3">
+        <v>327500</v>
+      </c>
+      <c r="V9" s="3">
         <v>321900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>309000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>290200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>327300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>291000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>291300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>313700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>274200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>230200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>244300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>218300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>226100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>220100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>182600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>168200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>186800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>175700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>164700</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>199800</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>184500</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>171800</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>185100</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1946500</v>
+      </c>
+      <c r="E10" s="3">
         <v>1788800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1808100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1752800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1738700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1658500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1775100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1632400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1594500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1496000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1491600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1485900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1982800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1360100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1312800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1335600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>924600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>891600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>955300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>874000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>860600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>821000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>820600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>791500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>952400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>704000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>595800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>697900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>572100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>546000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>587000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>499800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>453100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>506900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>444200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>438200</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>566400</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>444700</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>448300</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>519500</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,65 +1496,68 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-291600</v>
+      </c>
+      <c r="E14" s="3">
         <v>-382100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-770600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-47700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-57500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-64300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-507100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-466500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-286500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-58400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-191000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-218600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-209600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1300</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>18200</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
@@ -1545,186 +1565,192 @@
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>187500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>23700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>98300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>23600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>47800</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>13600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>2100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-100</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>2000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>1000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>37800</v>
       </c>
-      <c r="AL14" s="3">
-        <v>0</v>
-      </c>
       <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
         <v>30600</v>
       </c>
-      <c r="AN14" s="3">
-        <v>0</v>
-      </c>
       <c r="AO14" s="3">
         <v>0</v>
       </c>
       <c r="AP14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>689500</v>
+      </c>
+      <c r="E15" s="3">
         <v>731500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>668800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>648000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>657200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>652100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>656400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>649300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>637300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>637500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>638300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>642000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>602200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>602400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>612400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>401500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>402300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>396600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>396800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>390800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>392700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>397600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>417100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>400700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>398200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>346000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>289200</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>282300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>284400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>284000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>286800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>252700</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>203700</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>204100</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>222500</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>201900</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>228100</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>226600</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>225700</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>224900</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1465800</v>
+      </c>
+      <c r="E17" s="3">
         <v>1470700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1400400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1321300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1328700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1325500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1286500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1251900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1271100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1294100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1245400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1251200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1248800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1193600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1150000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>911600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>825300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>826500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>800000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>771200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>764500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>993800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>802300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>867700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>808100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>747200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>588500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>607600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>572900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>585800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>565900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>502900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>433700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>457500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>499300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>427400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>521500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>467300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>455900</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>470400</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1107200</v>
+      </c>
+      <c r="E18" s="3">
         <v>920300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>986500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>985400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>962900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>882100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1008200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>869300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>839200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>735000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>733300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>734900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1272800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>650800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>601600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>839300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>426800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>392600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>477200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>411800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>386300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>154500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>309300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>215100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>458000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>231000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>237500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>334600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>217500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>186300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>241200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>179500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>187600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>236200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>120600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>175500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>244700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>161900</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>164200</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>234200</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-109700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-44600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-68300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-101000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>122800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>31700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-146000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>37900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-37200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-63600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>15500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-68000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-26100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>157000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>332400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>329800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>920400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>926400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>509000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>381600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>342200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>116500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>210200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>124700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>396700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>270100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>229700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>279100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>261500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>530400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>274100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>247800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>218600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>292600</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>820000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>133400</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>141300</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>391000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>164300</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1906300</v>
+      </c>
+      <c r="E21" s="3">
         <v>1696400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1723500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1734400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1497300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1502500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1810600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1480600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1513600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1436100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1356200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1444800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1901100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1261800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1370900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1573200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1158900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1709700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1800500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1311600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1160700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>894300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>842800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>826100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>980900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>973700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>796800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>846600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>781000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>731800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1058300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>706400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>639100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>658900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>635700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1197500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>606300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>529800</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>781000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>623300</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>276300</v>
+      </c>
+      <c r="E22" s="3">
         <v>254300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>260500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>258300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>251900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>231800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>232200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>230100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>208300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>193300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>174500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>181100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>149800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>136000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>120800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>63900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>60300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>64100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>62900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>63600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>68400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>71300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>76900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>80700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>81300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>75600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>60100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>60200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>59100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>60500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>62400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>64200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>56300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>46300</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>62000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>64200</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>75400</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>72900</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>70600</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>75300</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1232100</v>
+      </c>
+      <c r="E23" s="3">
         <v>1092800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1564900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>875800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>645700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>682900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1429000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1067700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>954600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>663600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>734400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>840400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1358700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>530700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>637800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1107800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>696300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1248900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1340800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>857200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>699500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>425400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>348900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>344700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>501400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>552100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>447500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>504100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>437500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>387300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>709200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>389500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>379100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>408500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>351200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>931400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>302800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>230300</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>484700</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>323200</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>108200</v>
+      </c>
+      <c r="E24" s="3">
         <v>48000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>82700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>54500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>23400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>43400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>86900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>43100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>32800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>58500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>41200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>79200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>32100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>17700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>38700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>49800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>29200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>39900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>59400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>49200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>25700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>40900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>12200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>46500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>30900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>21300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>13100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>26600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>13500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>6700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>14000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>14100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>16600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>12300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>17900</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>14800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>9600</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>18000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1124000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1044800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1482200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>821300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>622300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>639500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1342200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1063500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>911500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>630800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>675900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>799100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1279500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>498600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>620100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1069200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>646400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1219700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1300900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>797700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>650300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>399700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>308000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>332500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>454900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>521200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>426200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>491000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>410800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>373800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>702500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>375500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>365000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>392000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>338900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>913400</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>288000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>220700</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>466700</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>307200</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1060800</v>
+      </c>
+      <c r="E27" s="3">
         <v>980500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1398200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>762900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>569700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>591500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1277400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1004300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>859800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>584300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>629500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>746200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1214600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>463200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>585800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1013900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>609900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1149300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1247100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>722000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>598600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>365800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>280500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>298700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>404500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>489400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>385500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>450600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>383800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>347000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>608600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>346300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>334600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>365900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>295500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>876200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>266900</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>203300</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>453100</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>287000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3239,15 +3300,15 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG29" s="3">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-12000</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3263,8 +3324,8 @@
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN29" s="3">
-        <v>0</v>
+      <c r="AN29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AO29" s="3">
         <v>0</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>109700</v>
+      </c>
+      <c r="E32" s="3">
         <v>44600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>68300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>101000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-122800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-31700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>146000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-37900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>37200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>63600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-15500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>68000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>26100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>8600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-157000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-332400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-329800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-920400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-926400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-509000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-381600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-342200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-116500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-210200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-124700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-396700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-270100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-229700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-279100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-261500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-530400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-274100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-247800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-218600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-292600</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-820000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-133400</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-141300</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-391000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-164300</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1062200</v>
+      </c>
+      <c r="E33" s="3">
         <v>982000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1399800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>764300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>571200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>593000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1278900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1005700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>861300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>585700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>630900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>747600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1216000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>464600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>585800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1013900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>609900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1149300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1247100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>722000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>598600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>365800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>280500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>298700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>404500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>489400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>385500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>450600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>383800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>347000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>596600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>346300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>334600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>365900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>295500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>876200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>266900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>203300</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>453100</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>287000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1062200</v>
+      </c>
+      <c r="E35" s="3">
         <v>982000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1399800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>764300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>571200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>593000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1278900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1005700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>861300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>585700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>630900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>747600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1216000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>464600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>585800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1013900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>609900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1149300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1247100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>722000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>598600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>365800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>280500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>298700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>404500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>489400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>385500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>450600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>383800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>347000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>596600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>346300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>334600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>365900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>295500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>876200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>266900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>203300</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>453100</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>287000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,175 +4305,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1765000</v>
+      </c>
+      <c r="E41" s="3">
         <v>861100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1145600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1186000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1066100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>671100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1318600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>780900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>598300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>500600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>530400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>740800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>531100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>522500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>278500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>636300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>437500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1912800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>556100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>585100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>601400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>676100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>598100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>940200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>549100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>807900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1088900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1025000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>401200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>251000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>343900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>275600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>527800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>458100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>447000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>568700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>271400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>395800</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>807300</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>375100</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E42" s="3">
         <v>10100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>200</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>9600</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>1400</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2800</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4463,56 +4553,59 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="3">
         <v>838500</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" s="3">
         <v>624500</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N43" s="3">
         <v>554300</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="Q43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R43" s="3">
         <v>521300</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
-      </c>
       <c r="S43" s="3">
         <v>0</v>
       </c>
@@ -4568,25 +4661,28 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL43" s="3">
         <v>34300</v>
       </c>
-      <c r="AL43" s="3">
-        <v>0</v>
-      </c>
       <c r="AM43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN43" s="3">
         <v>19500</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>17000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>32100</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4629,8 +4725,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4707,53 +4803,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>583600</v>
+      </c>
+      <c r="E45" s="3">
         <v>586600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>531000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>423400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>301000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>627900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>607700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>386800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>633100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>491600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>797500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>952600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>740600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>878800</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4829,53 +4928,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2350300</v>
+      </c>
+      <c r="E46" s="3">
         <v>1457800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2516700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1610500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1367300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1299000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2560300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1167600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1232800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>992200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1882300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1697300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1274700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1404100</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4951,252 +5053,261 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>11467400</v>
+      </c>
+      <c r="E47" s="3">
         <v>11241700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>11093900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>10543100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>10618200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>10287300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>10079400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>10092800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9764900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>9691100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>9544000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>9091800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>9931300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>9680100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>9815400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>8659100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>8443600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8679000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8611000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7652300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7811400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>7514800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>7602000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>7311000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>7201000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>6834800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>6237400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>5886800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>5813600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>5613100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>5745300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>5618200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>5414600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>5676000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>5496500</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>5371800</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>4617700</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>4305900</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>4230400</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>4580600</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>82030100</v>
+      </c>
+      <c r="E48" s="3">
         <v>80610300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>81293600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>81345400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>81181900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>80128300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>79408100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>80481100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>78574500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>78674600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>78626800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>77259200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>77299300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>73612300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>73442600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>47396300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>47019000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>45601500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>45337000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>45054400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>44413600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>43635500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>44338000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>43332300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>43145200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>42960100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>30273100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>30061000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>30204400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>29910800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>29930300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>29834300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>21271500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>21676800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>21779300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>21999500</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>23474900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>23216400</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>23361000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>23932000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5204,11 +5315,11 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>2216000</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
         <v>0</v>
       </c>
@@ -5216,11 +5327,11 @@
         <v>0</v>
       </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>1993700</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
@@ -5228,10 +5339,10 @@
         <v>0</v>
       </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>1935800</v>
-      </c>
-      <c r="N49" s="3">
-        <v>836600</v>
       </c>
       <c r="O49" s="3">
         <v>836600</v>
@@ -5240,11 +5351,11 @@
         <v>836600</v>
       </c>
       <c r="Q49" s="3">
+        <v>836600</v>
+      </c>
+      <c r="R49" s="3">
         <v>1183000</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
-      </c>
       <c r="S49" s="3">
         <v>0</v>
       </c>
@@ -5317,8 +5428,11 @@
       <c r="AP49" s="3">
         <v>0</v>
       </c>
+      <c r="AQ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5164100</v>
+      </c>
+      <c r="E52" s="3">
         <v>4823600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>639400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4842200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4549700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4278700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>423500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4163700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3965300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3952400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>280900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3064500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3050200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2987800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>776500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>614400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>403600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>373700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>669700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>571700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>692100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1055800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1070700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1757200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1948500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1975500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>720700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>799000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>609100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>900000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>622300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>761600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>892500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>473200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>342100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>321900</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>351000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>439700</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>322100</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>450300</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>101011900</v>
+      </c>
+      <c r="E54" s="3">
         <v>98133500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>98724300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>98341100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>97717100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>95993400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>95328900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>95905200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>93537400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>93310300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>93020800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>91949400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>92392000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>88520900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>87897400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>60945500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>59763800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>59779900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>58486200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>57016700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>56441400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>55732800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>56065000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>55759600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>55221900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>55007200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>40031900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>39448200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>38706800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>38392100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>38417700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>38268200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>29502900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>29671500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>29481100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>29654200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>30150400</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>29815000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>30249900</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>30888200</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,231 +6145,235 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2529600</v>
+      </c>
+      <c r="E57" s="3">
         <v>1681000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1963600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1847400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1628000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1620400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1769300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1808100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1647900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1752500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1766000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1721100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1582200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1507700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1711900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1318400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1042100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1206200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1252800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1441800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1304500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1138900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1143400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1119100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1140600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>888300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>705000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>808900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>740900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>695800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>760500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>873400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>719700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>692900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>702800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>707000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>554800</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>549800</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>556200</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>672100</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1071900</v>
+      </c>
+      <c r="E58" s="3">
         <v>1044200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1983000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>177100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>460300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>451500</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>2200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>105300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>127700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>59000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>31600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>32900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>294200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>324500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>792200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>985700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>94800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>41600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>281500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>376100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>15100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>29900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>535800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>13400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>15600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>252700</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ58" s="3">
-        <v>0</v>
+      <c r="AJ58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK58" s="3">
         <v>0</v>
@@ -6259,58 +6393,61 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E59" s="3">
         <v>21400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>41200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>75400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>104800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>21800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>63500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>21100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>25900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>49300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>43700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>32500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1073400</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S59" s="3">
-        <v>0</v>
+      <c r="S59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T59" s="3">
         <v>0</v>
@@ -6324,36 +6461,36 @@
       <c r="W59" s="3">
         <v>0</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y59" s="3">
+      <c r="X59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z59" s="3">
         <v>487000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>448500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>488600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>498100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>471600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>432100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>403200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>392300</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>8</v>
       </c>
@@ -6363,8 +6500,8 @@
       <c r="AJ59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK59" s="3">
-        <v>0</v>
+      <c r="AK59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AL59" s="3">
         <v>0</v>
@@ -6381,53 +6518,56 @@
       <c r="AP59" s="3">
         <v>0</v>
       </c>
+      <c r="AQ59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3623800</v>
+      </c>
+      <c r="E60" s="3">
         <v>2746700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4211700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2099900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2193100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2093700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1977700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1873900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1774300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1906100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2086400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1766400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1618100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1556500</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6503,211 +6643,217 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>36021800</v>
+      </c>
+      <c r="E61" s="3">
         <v>34266000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>33697500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>35745900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>34836700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>32444400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>31494600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>32912100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>30410000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>30044600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>29598100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>28163500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>28763400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>25764100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>23843000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>17845100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>17716300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>17576400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>16729300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>17040900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>16943700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>16222000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>16473000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>16516000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>15651700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>15646700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>11370100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>11445800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>10952700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>10453400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>11089800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>11232100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>9427100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>9460200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>9412600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>9721100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>11081900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>10966900</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>10608300</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>11257000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3246700</v>
+      </c>
+      <c r="E62" s="3">
         <v>3172300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2404900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3283300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3380400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3379900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2623400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3455200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3429800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3562500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3016900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3758600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3932700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3735100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>10600</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Y62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z62" s="3">
         <v>16200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>35500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>50500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>46500</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
@@ -6717,8 +6863,8 @@
       <c r="AF62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG62" s="3">
-        <v>0</v>
+      <c r="AG62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH62" s="3">
         <v>0</v>
@@ -6747,8 +6893,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>42892400</v>
+      </c>
+      <c r="E66" s="3">
         <v>40185000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>40970200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>41129000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>40410200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>37918000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>36712100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>38241100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>35614100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>35513200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>35197100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>33688500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>34314200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>31055700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>34660200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>25652400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>25188100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>25607800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>25059300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>24510600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>24335700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>23724300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>24093500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>23662400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>22978900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>22747800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>17378700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>16931000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>16375900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>16057600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>16119600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>16237600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>13864300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>13991400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>13849900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>14110400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>15303100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>15068100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>15258900</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>16089000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7598,7 +7766,7 @@
         <v>63900</v>
       </c>
       <c r="AA70" s="3">
-        <v>68900</v>
+        <v>63900</v>
       </c>
       <c r="AB70" s="3">
         <v>68900</v>
@@ -7631,7 +7799,7 @@
         <v>68900</v>
       </c>
       <c r="AL70" s="3">
-        <v>78200</v>
+        <v>68900</v>
       </c>
       <c r="AM70" s="3">
         <v>78200</v>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>78200</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>78200</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,8 +7938,11 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -7811,86 +7985,89 @@
       <c r="P72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R72" s="3">
         <v>-457700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-312900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-740800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-764400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1327800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-2108000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-2363300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-2495300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-2394700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-2245900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-2115700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-2090900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-2151200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-2201500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-2317000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-2366000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-2378500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-2672700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-2716200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-2794800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-2904500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-2965800</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-3607300</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-3640200</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-3610000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>-3828100</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>53661800</v>
+      </c>
+      <c r="E76" s="3">
         <v>53439500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>53129200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>52571600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>52664600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>53403300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>53887200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>53007800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>53281100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>53126700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>53117800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>53571900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>53401700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>52771300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>53173300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>35229200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>34511800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>34108100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>33362900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>32442200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>32041800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>31944600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>31907600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>32033200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>32174000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>32190500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>22584200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>22448300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>22261900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>22265500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>22229100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>21961700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>15569600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>15611100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>15562200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>15465500</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>14769100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>14668600</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>14912800</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>14720900</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1062200</v>
+      </c>
+      <c r="E81" s="3">
         <v>982000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1399800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>764300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>571200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>593000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1278900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1005700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>861300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>585700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>630900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>747600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1216000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>464600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>585800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1013900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>609900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1149300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1247100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>722000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>598600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>365800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>280500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>298700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>404500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>489400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>385500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>450600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>383800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>347000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>596600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>346300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>334600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>365900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>295500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>876200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>266900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>203300</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>453100</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>287000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>657200</v>
+      </c>
+      <c r="E83" s="3">
         <v>652100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>656400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>649300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>637300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>637500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>638300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>642000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>602200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>602400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>612400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>401500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>402300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>396600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>612400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>401500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>402300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>396600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>396800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>390800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>392700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>397600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>417100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>400700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>398200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>346000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>289200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>282300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>284400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>284000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>286800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>252700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>203700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>204100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>222500</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>201900</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>228100</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>226600</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>225700</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>224900</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1346900</v>
+      </c>
+      <c r="E89" s="3">
         <v>1288100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1158200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1447700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1241700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1160800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1335500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1434800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1086500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1055500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1074400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1969200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1215100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1114300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1277600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1203300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>804000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>841500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>716100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>814100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>649200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>816700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>603700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>978000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>676300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>679100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>616400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>644100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>508600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>494900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>529600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>500700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>424000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>349200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>326900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>615200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>392400</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>352800</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>420000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>363400</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,8 +9910,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9734,86 +9955,89 @@
       <c r="P91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R91" s="3">
         <v>-1240100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1194500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2278000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1109300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2064000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1197200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-33100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-8100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-58100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-39900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-37800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-13600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-53900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-47100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-28400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-13600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-30600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-29200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-10500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-41900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-31400</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-26400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-464200</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-629000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>310800</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1152600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-400600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>25100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1070100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1035000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1550500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>320000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1711100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-623800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1084100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1207300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-698900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3464000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1049200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1287600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1252500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2242400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>283400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1093500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-380600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-408900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-107100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-494500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-328700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-242000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2009200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-403100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-364000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-77900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>159600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-19700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-457300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-338600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>151900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>201400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>512400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-227000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>56500</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>521900</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-177900</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,8 +10455,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10266,86 +10500,89 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R96" s="3">
         <v>-730500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-586100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-586200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-585900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-467000</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-466600</v>
       </c>
       <c r="W96" s="3">
         <v>-466600</v>
       </c>
       <c r="X96" s="3">
+        <v>-466600</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-466500</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-429200</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-428900</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-429300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-429100</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-336700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-336600</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-336300</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-336100</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-303800</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-304300</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-257600</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-257700</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-235600</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-236500</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-235700</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-235100</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-224100</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-224000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>708300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1158300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1218300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-251700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>181900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-275600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1091600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>445100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-355800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-84000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1047700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2279500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>172400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-371500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>258300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-13500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>242500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>350500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-443800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-322700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-592300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-466200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-260300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-696000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1050400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-156200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>350500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-285300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-748600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-443000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-288800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-4300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-496000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-649300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-830900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-297400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-828900</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-496800</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-198600</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E101" s="3">
         <v>17800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-26100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>13700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-9100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>6400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-12900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-22000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>6500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>23700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-10500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-23200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>23700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-10500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-23200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-10800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-6100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>7700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-39300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>14900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>2100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>3000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>6800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-6800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>4700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-6800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-11300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>5900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-700</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>800</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>7600</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>8200</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-12900</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>903900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-284500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-40400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>119900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>395000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-647500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>537700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>182500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>97800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-29800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-210500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>209700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>8600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>244000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-357800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>198800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1475200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1356600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-29000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-16400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-74600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>78000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-342100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>391100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-258700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-281000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>63900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>623800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>150200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-92800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>68300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-252300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>69700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>11100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-121700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>297400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-124500</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-411500</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>432200</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>42900</v>
       </c>
     </row>
